--- a/output/pdf_financials_xlsx/MX.xlsx
+++ b/output/pdf_financials_xlsx/MX.xlsx
@@ -43819,7 +43819,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -47243,7 +47243,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E404" s="5" t="n">

--- a/output/pdf_financials_xlsx/MX.xlsx
+++ b/output/pdf_financials_xlsx/MX.xlsx
@@ -1328,25 +1328,25 @@
         <v>-128.533</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-283.92</v>
+        <v>55.92</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>85.27</v>
+        <v>-85.27</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-70.12</v>
+        <v>70.12</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-155.337</v>
+        <v>155.337</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-10.997</v>
+        <v>10.997</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>9.279</v>
+        <v>-9.279</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-95.788</v>
+        <v>95.788</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>153.491</v>
@@ -2310,7 +2310,7 @@
         <v>94.42554785815561</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>100</v>
+        <v>19.69568892645816</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-71.15023572113981</v>
@@ -5114,25 +5114,25 @@
         <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>190.528</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>628.6849999999999</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>618.8</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>761.427</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>751.389</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>695.461</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>642.054</v>
       </c>
     </row>
     <row r="79">
@@ -5172,25 +5172,25 @@
         <v>1502.271</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1458.286</v>
+        <v>1648.814</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>1768.853</v>
+        <v>2397.538</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2158.192</v>
+        <v>2776.992</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>2151.513</v>
+        <v>2912.94</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>2141.801</v>
+        <v>2893.19</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>2414.935</v>
+        <v>3110.396</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>2752.9</v>
+        <v>3394.954</v>
       </c>
     </row>
     <row r="80">
@@ -5234,25 +5234,25 @@
         <v>0.8608455278775963</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.806645053409011</v>
+        <v>0.9120348526225481</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>1.084946269535563</v>
+        <v>1.470557422900464</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>1.104086444631</v>
+        <v>1.420651741850925</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.8855941883309727</v>
+        <v>1.199008667368881</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.9856347189184438</v>
+        <v>1.331416183122359</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>1.01413911759543</v>
+        <v>1.306194268091007</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>1.009623865690576</v>
+        <v>1.245096654917245</v>
       </c>
     </row>
     <row r="81">
@@ -5534,25 +5534,25 @@
         <v>615.412</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>295.519</v>
+        <v>104.991</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>1149.156</v>
+        <v>520.471</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>1013.479</v>
+        <v>394.679</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>1107.893</v>
+        <v>346.466</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>809.431</v>
+        <v>58.042</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>1071.309</v>
+        <v>375.848</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>1081.36</v>
+        <v>439.306</v>
       </c>
     </row>
     <row r="86">
@@ -6779,10 +6779,10 @@
         <v>-19.018</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>-23.505</v>
+        <v>9.988</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>-24</v>
+        <v>54.821</v>
       </c>
       <c r="L107" s="3" t="n">
         <v>-59.444</v>
@@ -6794,10 +6794,10 @@
         <v>-10.53</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>-20.503</v>
+        <v>-5.105</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>-37.894</v>
+        <v>-3.392</v>
       </c>
       <c r="Q107" s="3" t="n">
         <v>-33.805</v>
@@ -7585,31 +7585,31 @@
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-252.644</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-146.283</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-286.12</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-444.414</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-52.805</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-62.898</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-252.985</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-86.392</v>
       </c>
       <c r="Q121" s="3" t="n">
         <v>0</v>
@@ -10002,7 +10002,11 @@
           <t>Lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -23324,7 +23328,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -23494,7 +23502,11 @@
           <t>Payments for repurchase of shares</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -25165,7 +25177,11 @@
           <t>Payments for repurchase of shares</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -27467,7 +27483,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -29041,7 +29061,11 @@
           <t>Payments for repurchase of shares</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -31137,7 +31161,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -33119,7 +33147,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" s="5" t="n">
         <v>-39.41</v>
       </c>
@@ -40279,7 +40311,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
